--- a/Project_CSD/Assets/Temp/DataBase/PlayerInfoDB.xlsx
+++ b/Project_CSD/Assets/Temp/DataBase/PlayerInfoDB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SCHALE\Documents\GitHub\Capstone-Design\Project_CSD\Assets\Temp\DataBase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263660EB-6C7B-43E8-BB24-E5CCDC2D2544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69059A3-6A03-4F38-AAB4-8BCBD50A5E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Player_No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,11 +66,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Player</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Admin</t>
+    <t>Score</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -396,13 +392,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -424,22 +420,25 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>8000100</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1234</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -447,8 +446,11 @@
       <c r="G2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>0</v>
       </c>
@@ -468,6 +470,217 @@
         <v>0</v>
       </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
     </row>
